--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>起始單號</t>
   </si>
@@ -65,19 +65,10 @@
     <t>耀成</t>
   </si>
   <si>
-    <t>KT0000000001</t>
-  </si>
-  <si>
-    <t>KT9999999999</t>
-  </si>
-  <si>
     <t>嘉里大榮</t>
   </si>
   <si>
-    <t>KT062026050008</t>
-  </si>
-  <si>
-    <t>大榮大宗海運跨境件</t>
+    <t>深圳</t>
   </si>
   <si>
     <t>802048446001</t>
@@ -727,8 +718,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1103,10 +1097,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
@@ -1120,10 +1114,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
@@ -1137,28 +1131,28 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" t="s">
+      <c r="A4">
+        <v>40552382701</v>
+      </c>
+      <c r="B4">
+        <v>40552445200</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4">
+        <v>11000013</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -1167,15 +1161,15 @@
         <v>9045214502</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -1184,15 +1178,15 @@
         <v>9045214504</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -1201,15 +1195,15 @@
         <v>9045214507</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>27</v>
+      <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
@@ -1218,7 +1212,7 @@
         <v>9045214506</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>起始單號</t>
   </si>
@@ -44,6 +44,9 @@
     <t>財務/合約備註</t>
   </si>
   <si>
+    <t>黑貓API授權碼</t>
+  </si>
+  <si>
     <t>802050446001</t>
   </si>
   <si>
@@ -105,6 +108,9 @@
   </si>
   <si>
     <t>超峰菜鳥</t>
+  </si>
+  <si>
+    <t>vktjowcr</t>
   </si>
 </sst>
 </file>
@@ -1070,8 +1076,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -1079,7 +1085,7 @@
     <col min="4" max="4" width="11.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1095,42 +1101,45 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>9353865110</v>
       </c>
       <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
       </c>
       <c r="D3">
         <v>9353865112</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>40552382701</v>
       </c>
@@ -1138,81 +1147,84 @@
         <v>40552445200</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>11000013</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>9045214502</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>9045214504</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>9045214507</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>9045214506</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>起始單號</t>
   </si>
@@ -111,6 +111,15 @@
   </si>
   <si>
     <t>vktjowcr</t>
+  </si>
+  <si>
+    <t>802021446006</t>
+  </si>
+  <si>
+    <t>802023445994</t>
+  </si>
+  <si>
+    <t>深圳線上</t>
   </si>
 </sst>
 </file>
@@ -1076,8 +1085,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -1227,6 +1236,23 @@
         <v>27</v>
       </c>
     </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>9045214510</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>起始單號</t>
   </si>
@@ -120,6 +120,15 @@
   </si>
   <si>
     <t>深圳線上</t>
+  </si>
+  <si>
+    <t>義烏</t>
+  </si>
+  <si>
+    <t>雄麻吉</t>
+  </si>
+  <si>
+    <t>廈門台星</t>
   </si>
 </sst>
 </file>
@@ -733,8 +742,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1085,7 +1097,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1115,10 +1127,10 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
@@ -1132,10 +1144,10 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
@@ -1166,10 +1178,10 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
@@ -1183,10 +1195,10 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
@@ -1200,10 +1212,10 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
@@ -1217,10 +1229,10 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
@@ -1237,10 +1249,10 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
@@ -1251,6 +1263,74 @@
       </c>
       <c r="E9" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2">
+        <v>40552445201</v>
+      </c>
+      <c r="B10" s="2">
+        <v>40552507700</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>11000062</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>40552507701</v>
+      </c>
+      <c r="B11">
+        <v>40552549367</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>11000092</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>40552549368</v>
+      </c>
+      <c r="B12">
+        <v>40552591034</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>11000043</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>40552332701</v>
+      </c>
+      <c r="B13">
+        <v>40552382700</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>11000063</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>起始單號</t>
   </si>
@@ -129,6 +129,12 @@
   </si>
   <si>
     <t>廈門台星</t>
+  </si>
+  <si>
+    <t>802019446006</t>
+  </si>
+  <si>
+    <t>802021445992</t>
   </si>
 </sst>
 </file>
@@ -742,11 +748,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1097,7 +1100,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1127,10 +1130,10 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
@@ -1144,10 +1147,10 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
@@ -1178,10 +1181,10 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
@@ -1195,10 +1198,10 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
@@ -1212,10 +1215,10 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
@@ -1229,10 +1232,10 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
@@ -1249,10 +1252,10 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
@@ -1266,10 +1269,10 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>40552445201</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>40552507700</v>
       </c>
       <c r="C10" t="s">
@@ -1278,7 +1281,7 @@
       <c r="D10">
         <v>11000062</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1331,6 +1334,23 @@
       </c>
       <c r="E13" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <v>9045214507</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="41">
   <si>
     <t>起始單號</t>
   </si>
@@ -135,6 +135,21 @@
   </si>
   <si>
     <t>802021445992</t>
+  </si>
+  <si>
+    <t>801948146006</t>
+  </si>
+  <si>
+    <t>801948645990</t>
+  </si>
+  <si>
+    <t>ec</t>
+  </si>
+  <si>
+    <t>802041446001</t>
+  </si>
+  <si>
+    <t>802042445995</t>
   </si>
 </sst>
 </file>
@@ -147,12 +162,19 @@
     <numFmt numFmtId="176" formatCode="_-&quot;NT$&quot;* #,##0.00_-;\-&quot;NT$&quot;* #,##0.00_-;_-&quot;NT$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;NT$&quot;* #,##0_-;\-&quot;NT$&quot;* #,##0_-;_-&quot;NT$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -618,139 +640,142 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -1100,7 +1125,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1130,10 +1155,10 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
@@ -1147,10 +1172,10 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
@@ -1181,10 +1206,10 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
@@ -1198,10 +1223,10 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
@@ -1215,10 +1240,10 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
@@ -1232,10 +1257,10 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
@@ -1252,10 +1277,10 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
@@ -1337,10 +1362,10 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
@@ -1351,6 +1376,57 @@
       </c>
       <c r="E14" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15">
+        <v>9045214507</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16">
+        <v>9353865116</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" ht="15.6" spans="1:5">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <v>9045214509</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
   <si>
     <t>起始單號</t>
   </si>
@@ -150,6 +150,12 @@
   </si>
   <si>
     <t>802042445995</t>
+  </si>
+  <si>
+    <t>802067446002</t>
+  </si>
+  <si>
+    <t>802069445990</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1429,6 +1435,23 @@
         <v>14</v>
       </c>
     </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>9045214507</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="46">
   <si>
     <t>起始單號</t>
   </si>
@@ -156,6 +156,15 @@
   </si>
   <si>
     <t>802069445990</t>
+  </si>
+  <si>
+    <t>802044446004</t>
+  </si>
+  <si>
+    <t>802046445992</t>
+  </si>
+  <si>
+    <t>穩達達</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1452,6 +1461,23 @@
         <v>23</v>
       </c>
     </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <v>9353865126</v>
+      </c>
+      <c r="E19" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
   <si>
     <t>起始單號</t>
   </si>
@@ -165,6 +165,15 @@
   </si>
   <si>
     <t>穩達達</t>
+  </si>
+  <si>
+    <t>802046446006</t>
+  </si>
+  <si>
+    <t>802048445994</t>
+  </si>
+  <si>
+    <t>天馬</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1478,6 +1487,23 @@
         <v>45</v>
       </c>
     </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20">
+        <v>9353865130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\超峰號段系統\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="50">
   <si>
     <t>起始單號</t>
   </si>
@@ -174,6 +179,9 @@
   </si>
   <si>
     <t>天馬</t>
+  </si>
+  <si>
+    <t>首波</t>
   </si>
 </sst>
 </file>
@@ -794,12 +802,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -1149,7 +1160,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1179,10 +1190,10 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
@@ -1196,10 +1207,10 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
@@ -1230,10 +1241,10 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
@@ -1247,10 +1258,10 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
@@ -1264,10 +1275,10 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
@@ -1281,10 +1292,10 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
@@ -1301,10 +1312,10 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
@@ -1386,10 +1397,10 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
@@ -1403,10 +1414,10 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
@@ -1420,10 +1431,10 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
@@ -1454,10 +1465,10 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C18" t="s">
@@ -1471,10 +1482,10 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C19" t="s">
@@ -1488,10 +1499,10 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C20" t="s">
@@ -1502,6 +1513,40 @@
       </c>
       <c r="E20" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>40552591035</v>
+      </c>
+      <c r="B21" s="3">
+        <v>40552611034</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21">
+        <v>11000013</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>40552611035</v>
+      </c>
+      <c r="B22" s="3">
+        <v>40552632700</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22">
+        <v>11000083</v>
+      </c>
+      <c r="E22" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
   <si>
     <t>起始單號</t>
   </si>
@@ -802,15 +802,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -866,6 +863,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1160,7 +1166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1190,10 +1196,10 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
@@ -1207,10 +1213,10 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
@@ -1241,10 +1247,10 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
@@ -1258,10 +1264,10 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
@@ -1275,10 +1281,10 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
@@ -1292,10 +1298,10 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
@@ -1312,10 +1318,10 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
@@ -1397,10 +1403,10 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
@@ -1414,142 +1420,128 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>22</v>
+      <c r="A15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
       </c>
       <c r="D15">
-        <v>9045214507</v>
+        <v>9353865116</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" ht="15.6" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
       </c>
       <c r="D16">
-        <v>9353865116</v>
-      </c>
-      <c r="E16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" ht="15.6" spans="1:5">
-      <c r="A17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>9045214509</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
       </c>
       <c r="D17">
-        <v>9045214509</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>9045214507</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>42</v>
+      <c r="A18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18">
-        <v>9045214507</v>
+        <v>9353865126</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>44</v>
+      <c r="A19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
       </c>
       <c r="D19">
-        <v>9353865126</v>
+        <v>9353865130</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>47</v>
+      <c r="A20" s="1">
+        <v>40552591035</v>
+      </c>
+      <c r="B20" s="1">
+        <v>40552611034</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D20">
-        <v>9353865130</v>
-      </c>
-      <c r="E20" t="s">
-        <v>48</v>
+        <v>11000013</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3">
-        <v>40552591035</v>
-      </c>
-      <c r="B21" s="3">
-        <v>40552611034</v>
+      <c r="A21" s="1">
+        <v>40552611035</v>
+      </c>
+      <c r="B21" s="1">
+        <v>40552632700</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
       </c>
       <c r="D21">
-        <v>11000013</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3">
-        <v>40552611035</v>
-      </c>
-      <c r="B22" s="3">
-        <v>40552632700</v>
-      </c>
-      <c r="C22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22">
         <v>11000083</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E21" t="s">
         <v>49</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A21 A23:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
   <si>
     <t>起始單號</t>
   </si>
@@ -179,9 +179,6 @@
   </si>
   <si>
     <t>天馬</t>
-  </si>
-  <si>
-    <t>首波</t>
   </si>
 </sst>
 </file>
@@ -1532,10 +1529,10 @@
         <v>13</v>
       </c>
       <c r="D21">
-        <v>11000083</v>
-      </c>
-      <c r="E21" t="s">
-        <v>49</v>
+        <v>11000013</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
   <si>
     <t>起始單號</t>
   </si>
@@ -1163,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1535,6 +1535,23 @@
         <v>14</v>
       </c>
     </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>40558262701</v>
+      </c>
+      <c r="B22">
+        <v>40558282700</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22">
+        <v>11000013</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A21 A23:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/號段維護表.xlsx
+++ b/號段維護表.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="49">
   <si>
     <t>起始單號</t>
   </si>
@@ -1163,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1552,6 +1552,23 @@
         <v>14</v>
       </c>
     </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>40558282701</v>
+      </c>
+      <c r="B23">
+        <v>40558362700</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23">
+        <v>11000013</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A21 A23:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
